--- a/p6_deployment/data/england/missing/data_understanding/all/df_match_miss.xlsx
+++ b/p6_deployment/data/england/missing/data_understanding/all/df_match_miss.xlsx
@@ -756,10 +756,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Emirates Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>60 704</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60 312</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2</t>
@@ -1016,10 +1034,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Brentford Community Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>17 250</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>17 124</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1276,10 +1312,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>31 662</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1544,10 +1598,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Scott G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Turf Moor
+ (Burnley)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22 546</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>21 109</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1804,10 +1876,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>39 724</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2</t>
@@ -2064,10 +2154,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bond D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25 191</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>5</t>
@@ -2324,10 +2432,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kavanagh C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Anfield
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>61 276</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60 059</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>2</t>
@@ -2592,10 +2718,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12 027</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>2</t>
@@ -2852,10 +2996,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>3</t>
@@ -3112,10 +3274,28 @@
           <t>19.05.2024 12:00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>32 050</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>29 116</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>0</t>
@@ -3372,9 +3552,23 @@
           <t>15.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
@@ -3632,10 +3826,28 @@
           <t>15.05.2024 15:45</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Salisbury M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>31 555</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>1</t>
@@ -3900,10 +4112,28 @@
           <t>14.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kavanagh C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61 065</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>0</t>
@@ -4160,10 +4390,28 @@
           <t>13.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Villa Park
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42 789</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>42 241</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>3</t>
@@ -4420,10 +4668,28 @@
           <t>12.05.2024 12:30</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>73 600</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>0</t>
@@ -4680,10 +4946,28 @@
           <t>11.05.2024 13:30</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Harrington T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>29 708</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>2</t>
@@ -4940,10 +5224,28 @@
           <t>11.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>11 154</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>1</t>
@@ -5200,10 +5502,28 @@
           <t>11.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>39 221</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>1</t>
@@ -5460,10 +5780,28 @@
           <t>11.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>51 997</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>1</t>
@@ -5720,10 +6058,28 @@
           <t>11.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61 148</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>2</t>
@@ -5980,10 +6336,28 @@
           <t>11.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>62 475</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>3</t>
@@ -6240,10 +6614,28 @@
           <t>11.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bramall T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>31 424</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>1</t>
@@ -6508,10 +6900,28 @@
           <t>11.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>24 418</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>0</t>
@@ -6776,10 +7186,28 @@
           <t>06.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>25 190</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>4</t>
@@ -7036,10 +7464,28 @@
           <t>05.05.2024 12:30</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Anfield
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>61 276</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>60 075</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>4</t>
@@ -7296,10 +7742,28 @@
           <t>05.05.2024 10:00</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>31 596</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>1</t>
@@ -7556,10 +8020,28 @@
           <t>05.05.2024 10:00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>39 295</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>5</t>
@@ -7816,9 +8298,23 @@
           <t>04.05.2024 13:30</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -8076,10 +8572,28 @@
           <t>04.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Scott G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Brentford Community Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>17 250</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>17 090</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>0</t>
@@ -8336,10 +8850,28 @@
           <t>04.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Turf Moor
+ (Burnley)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>22 546</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>21 781</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>1</t>
@@ -8596,10 +9128,28 @@
           <t>04.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kavanagh C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>32 050</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>28 516</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>1</t>
@@ -8864,10 +9414,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Coote D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Emirates Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>60 704</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>60 348</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>3</t>
@@ -9124,10 +9692,28 @@
           <t>03.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>11 873</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>1</t>
@@ -9384,10 +9970,28 @@
           <t>02.05.2024 15:30</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>2</t>
@@ -9644,10 +10248,28 @@
           <t>28.04.2024 12:30</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>29 677</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>0</t>
@@ -9896,10 +10518,28 @@
           <t>28.04.2024 10:00</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>11 188</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>3</t>
@@ -10156,10 +10796,28 @@
           <t>28.04.2024 10:00</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61 554</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>2</t>
@@ -10416,10 +11074,28 @@
           <t>27.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Villa Park
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>42 789</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>42 354</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>2</t>
@@ -10676,10 +11352,28 @@
           <t>27.04.2024 13:30</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>39 098</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>1</t>
@@ -10936,10 +11630,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>24 142</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>1</t>
@@ -11196,10 +11908,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>73 571</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>1</t>
@@ -11456,10 +12186,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Harrington T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>52 196</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>5</t>
@@ -11708,10 +12456,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Coote D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>31 531</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>2</t>
@@ -11968,10 +12734,28 @@
           <t>27.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>62 474</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>2</t>
@@ -12228,10 +13012,28 @@
           <t>25.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>31 596</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>0</t>
@@ -12488,10 +13290,28 @@
           <t>24.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bramall T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>25 002</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>2</t>
@@ -12748,10 +13568,28 @@
           <t>24.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>38 222</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>2</t>
@@ -13008,10 +13846,28 @@
           <t>24.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Salisbury M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>73 549</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>4</t>
@@ -13268,10 +14124,28 @@
           <t>24.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>25 541</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>0</t>
@@ -13536,10 +14410,28 @@
           <t>23.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Emirates Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>60 704</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60 238</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>5</t>
@@ -13796,10 +14688,28 @@
           <t>21.04.2024 12:30</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>24 401</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>1</t>
@@ -14056,9 +14966,23 @@
           <t>21.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Villa Park
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>42 789</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
@@ -14316,10 +15240,28 @@
           <t>21.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Scott G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>25 145</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>5</t>
@@ -14576,10 +15518,28 @@
           <t>21.04.2024 09:30</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>39 239</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>2</t>
@@ -14836,10 +15796,28 @@
           <t>20.04.2024 15:30</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>31 621</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>0</t>
@@ -15096,10 +16074,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>11 877</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>1</t>
@@ -15356,10 +16352,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>32 050</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>28 964</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>1</t>
@@ -15616,10 +16630,28 @@
           <t>15.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>39 392</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>6</t>
@@ -15876,10 +16908,28 @@
           <t>14.04.2024 12:30</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Coote D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Emirates Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>60 704</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>60 350</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>0</t>
@@ -16136,10 +17186,28 @@
           <t>14.04.2024 10:00</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Kavanagh C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Anfield
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>61 276</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60 090</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>0</t>
@@ -16396,10 +17464,28 @@
           <t>14.04.2024 10:00</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>62 459</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>0</t>
@@ -16656,10 +17742,28 @@
           <t>13.04.2024 13:30</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Harrington T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>11 229</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>2</t>
@@ -16916,10 +18020,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Brentford Community Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>17 250</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>17 115</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>2</t>
@@ -17176,10 +18298,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Turf Moor
+ (Burnley)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>22 546</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>20 687</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>1</t>
@@ -17436,10 +18576,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>53 449</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>5</t>
@@ -17696,10 +18854,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>29 604</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>2</t>
@@ -17956,10 +19132,28 @@
           <t>13.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>52 206</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>4</t>
@@ -18216,10 +19410,28 @@
           <t>07.04.2024 14:00</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61 098</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>3</t>
@@ -18476,10 +19688,28 @@
           <t>07.04.2024 13:30</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>32 050</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>28 638</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>2</t>
@@ -18736,10 +19966,28 @@
           <t>07.04.2024 11:30</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>73 522</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>2</t>
@@ -18988,10 +20236,28 @@
           <t>06.04.2024 13:30</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>31 677</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>0</t>
@@ -19248,9 +20514,23 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Salisbury M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Villa Park
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>42 789</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
@@ -19508,10 +20788,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>39 125</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>1</t>
@@ -19776,10 +21074,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>24 418</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>0</t>
@@ -20036,10 +21352,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>11 797</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>2</t>
@@ -20288,10 +21622,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Harrington T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>31 504</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>1</t>
@@ -20548,10 +21900,28 @@
           <t>06.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>25 132</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>2</t>
@@ -20808,10 +22178,28 @@
           <t>04.04.2024 16:15</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>39 694</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>4</t>
@@ -21068,10 +22456,28 @@
           <t>04.04.2024 15:30</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Anfield
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>61 276</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>60 055</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>3</t>
@@ -21328,10 +22734,28 @@
           <t>03.04.2024 16:15</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>53 422</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>4</t>
@@ -21588,10 +23012,28 @@
           <t>03.04.2024 15:30</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Emirates Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>60 704</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>60 262</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>2</t>
@@ -21848,10 +23290,28 @@
           <t>03.04.2024 15:30</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Brentford Community Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>17 250</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>17 024</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>0</t>
@@ -22108,10 +23568,28 @@
           <t>02.04.2024 16:15</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>62 469</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>1</t>
@@ -22368,10 +23846,28 @@
           <t>02.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Scott G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>11 207</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>1</t>
@@ -22628,10 +24124,28 @@
           <t>02.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Bramall T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Turf Moor
+ (Burnley)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>22 546</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>21 528</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>1</t>
@@ -22888,10 +24402,28 @@
           <t>02.04.2024 15:30</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Harrington T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>52 135</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>1</t>
@@ -23148,10 +24680,28 @@
           <t>02.04.2024 15:30</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>28 997</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>3</t>
@@ -23408,10 +24958,28 @@
           <t>31.03.2024 12:30</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>53 422</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>0</t>
@@ -23668,10 +25236,28 @@
           <t>31.03.2024 10:00</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Coote D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Anfield
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>61 276</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60 061</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>2</t>
@@ -23928,10 +25514,28 @@
           <t>30.03.2024 17:00</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Brentford Community Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>17 250</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>17 138</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>1</t>
@@ -24188,9 +25792,23 @@
           <t>30.03.2024 14:30</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Villa Park
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>42 789</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
@@ -24448,10 +26066,28 @@
           <t>30.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>11 207</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>2</t>
@@ -24708,10 +26344,28 @@
           <t>30.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>39 535</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>2</t>
@@ -24976,10 +26630,28 @@
           <t>30.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Kavanagh C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>29 520</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>1</t>
@@ -25236,10 +26908,28 @@
           <t>30.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>32 050</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>30 010</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>3</t>
@@ -25496,10 +27186,28 @@
           <t>30.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61 534</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>2</t>
@@ -25756,10 +27464,28 @@
           <t>30.03.2024 09:30</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>52 199</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>4</t>
@@ -26024,10 +27750,28 @@
           <t>17.03.2024 11:00</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>62 461</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>1</t>
@@ -26284,10 +28028,28 @@
           <t>16.03.2024 14:30</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>24 410</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>3</t>
@@ -26544,10 +28306,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bond D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Turf Moor
+ (Burnley)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>22 546</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>20 431</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>2</t>
@@ -26812,10 +28592,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>11 630</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>1</t>
@@ -27072,10 +28870,28 @@
           <t>13.03.2024 16:30</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>11 198</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>4</t>
@@ -27332,10 +29148,28 @@
           <t>11.03.2024 17:00</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>38 752</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>3</t>
@@ -27592,10 +29426,28 @@
           <t>10.03.2024 12:45</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Anfield
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>61 276</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>59 947</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>1</t>
@@ -27852,10 +29704,28 @@
           <t>10.03.2024 11:00</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Salisbury M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>31 505</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>1</t>
@@ -28112,10 +29982,28 @@
           <t>10.03.2024 11:00</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>62 441</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>2</t>
@@ -28372,9 +30260,23 @@
           <t>10.03.2024 10:00</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Kavanagh C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Villa Park
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>42 789</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
@@ -28640,10 +30542,28 @@
           <t>09.03.2024 14:30</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Emirates Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>60 704</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>60 331</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>2</t>
@@ -28900,10 +30820,28 @@
           <t>09.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>11 074</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>2</t>
@@ -29160,10 +31098,28 @@
           <t>09.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Gill S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>25 103</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>1</t>
@@ -29420,10 +31376,28 @@
           <t>09.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Harrington T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>30 860</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>2</t>
@@ -29680,10 +31654,28 @@
           <t>09.03.2024 09:30</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>73 601</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>2</t>
@@ -29940,10 +31932,28 @@
           <t>04.03.2024 17:00</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>32 050</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>29 980</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>0</t>
@@ -30200,10 +32210,28 @@
           <t>03.03.2024 12:30</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>3</t>
@@ -30460,10 +32488,28 @@
           <t>03.03.2024 10:00</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Coote D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Turf Moor
+ (Burnley)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>22 546</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>19 713</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>0</t>
@@ -30720,10 +32766,28 @@
           <t>02.03.2024 14:30</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>11 594</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>2</t>
@@ -30980,10 +33044,28 @@
           <t>02.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Brentford Community Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>17 250</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>17 140</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>2</t>
@@ -31240,10 +33322,28 @@
           <t>02.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>39 262</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>1</t>
@@ -31500,10 +33600,28 @@
           <t>02.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>24 460</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>3</t>
@@ -31760,10 +33878,28 @@
           <t>02.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>52 206</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>3</t>
@@ -32020,10 +34156,28 @@
           <t>02.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tierney P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>29 603</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>0</t>
@@ -32280,10 +34434,28 @@
           <t>02.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>61 339</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>3</t>
@@ -32540,10 +34712,28 @@
           <t>25.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Wembley Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>90 000</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>84 814</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>1</t>
@@ -32833,10 +35023,28 @@
           <t>21.04.2024 11:30</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Wembley Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>90 000</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>83 672</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>3</t>
@@ -33126,10 +35334,28 @@
           <t>20.04.2024 13:15</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Wembley Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>90 000</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>80 902</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>1</t>
@@ -33419,10 +35645,28 @@
           <t>17.03.2024 12:30</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>72 291</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>4</t>
@@ -33720,10 +35964,28 @@
           <t>17.03.2024 09:45</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>39 589</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
           <t>4</t>
@@ -34021,10 +36283,28 @@
           <t>16.03.2024 14:30</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>52 126</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>2</t>
@@ -34314,10 +36594,28 @@
           <t>16.03.2024 09:15</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>31 262</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>2</t>
@@ -34607,10 +36905,28 @@
           <t>26.05.2024 11:00</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Brooks J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Wembley Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>90 000</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>85 862</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>0</t>
@@ -34844,10 +37160,28 @@
           <t>17.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>30 712</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
           <t>3</t>
@@ -35081,10 +37415,28 @@
           <t>16.05.2024 16:00</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>36 384</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t>4</t>
@@ -35318,10 +37670,28 @@
           <t>12.05.2024 10:15</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>The Hawthorns
+ (West Bromwich)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>26 688</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>25 367</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>0</t>
@@ -35554,10 +37924,28 @@
           <t>12.05.2024 08:00</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Carrow Road
+ (Norwich)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>27 137</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>26 982</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>0</t>
@@ -35790,10 +38178,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>St. Andrew's Stadium
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>29 409</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>27 680</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>1</t>
@@ -36026,10 +38432,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Coventry Building Society Arena
+ (Coventry)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>32 753</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>29 102</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
           <t>1</t>
@@ -36262,10 +38686,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Portman Road
+ (Ipswich)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>29 673</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>29 011</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>2</t>
@@ -36498,10 +38940,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>36 766</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>1</t>
@@ -36734,10 +39194,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>32 261</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>32 117</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>0</t>
@@ -36970,10 +39448,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>28 289</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>3</t>
@@ -37206,10 +39702,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Bond D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Home Park
+ (Plymouth)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>16 881</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>1</t>
@@ -37434,10 +39948,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Davies A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Aesseal New York Stadium
+ (Rotherham)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>12 021</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>10 547</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>5</t>
@@ -37670,10 +40202,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>28 243</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>4</t>
@@ -37898,10 +40448,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Stadium of Light
+ (Sunderland)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>48 707</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>41 222</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
           <t>0</t>
@@ -38134,10 +40702,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Eltringham G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>17 661</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>0</t>
@@ -38378,10 +40964,28 @@
           <t>04.05.2024 08:30</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Martin S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>The Hawthorns
+ (West Bromwich)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>26 688</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>25 386</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr">
         <is>
           <t>3</t>
@@ -38614,10 +41218,31 @@
           <t>30.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)
+ - 
+Whitestone D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Coventry Building Society Arena
+ (Coventry)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>32 753</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>26 457</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
           <t>1</t>
@@ -38850,10 +41475,28 @@
           <t>29.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>19 641</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>0</t>
@@ -39086,10 +41729,28 @@
           <t>27.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>25 586</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>24 298</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr">
         <is>
           <t>3</t>
@@ -39322,10 +41983,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Backhouse A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>20 026</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
           <t>0</t>
@@ -39566,10 +42245,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Breakspear C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ashton Gate Stadium
+ (Bristol)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>22 873</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
           <t>2</t>
@@ -39802,10 +42499,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Simpson J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>22 999</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr">
         <is>
           <t>1</t>
@@ -40030,10 +42745,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>John Smith's Stadium
+ (Huddersfield)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>24 121</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>22 001</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>1</t>
@@ -40266,10 +42999,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Davies A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>17 863</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
           <t>1</t>
@@ -40494,10 +43245,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Linington J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Carrow Road
+ (Norwich)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>27 137</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>26 429</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
           <t>2</t>
@@ -40730,10 +43499,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Scott G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Hillsborough
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>39 732</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>33 295</t>
+        </is>
+      </c>
       <c r="G157" t="inlineStr">
         <is>
           <t>3</t>
@@ -40966,10 +43753,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>30 584</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
           <t>0</t>
@@ -41202,10 +44007,28 @@
           <t>27.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>22 200</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>20 712</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>1</t>
@@ -41438,10 +44261,28 @@
           <t>26.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Bond D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>16 677</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
           <t>4</t>
@@ -41674,10 +44515,28 @@
           <t>24.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Coventry Building Society Arena
+ (Coventry)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>32 753</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>25 023</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
           <t>2</t>
@@ -41910,10 +44769,28 @@
           <t>23.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Madley R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>32 261</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>31 872</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>5</t>
@@ -42146,10 +45023,28 @@
           <t>22.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Harrington T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>29 333</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
           <t>3</t>
@@ -42382,10 +45277,28 @@
           <t>21.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>21 718</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
           <t>1</t>
@@ -42618,10 +45531,28 @@
           <t>20.04.2024 13:15</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>16 464</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>1</t>
@@ -42854,10 +45785,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>22 372</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
           <t>2</t>
@@ -43090,10 +46039,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Busby J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>John Smith's Stadium
+ (Huddersfield)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>24 121</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>18 935</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>0</t>
@@ -43326,10 +46293,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Carrow Road
+ (Norwich)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>27 137</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>26 295</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
           <t>1</t>
@@ -43562,10 +46547,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Stroud K.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Aesseal New York Stadium
+ (Rotherham)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>12 021</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>11 001</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>0</t>
@@ -43798,10 +46801,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Madley R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>24 674</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
           <t>3</t>
@@ -44034,10 +47055,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Backhouse A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Stadium of Light
+ (Sunderland)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>48 707</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>40 743</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
           <t>0</t>
@@ -44270,10 +47309,28 @@
           <t>20.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Toner B.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>22 200</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>18 753</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t>0</t>
@@ -44506,10 +47563,28 @@
           <t>20.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Bramall T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>32 261</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>31 874</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
           <t>2</t>
@@ -44742,10 +47817,28 @@
           <t>16.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>27 636</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
           <t>3</t>
@@ -44978,10 +48071,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Bramall T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>St. Andrew's Stadium
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>29 409</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>26 811</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t>3</t>
@@ -45214,10 +48325,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Welch R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Ashton Gate Stadium
+ (Bristol)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>21 003</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t>1</t>
@@ -45450,10 +48579,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Nield T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>25 586</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>21 225</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
           <t>3</t>
@@ -45686,10 +48833,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Portman Road
+ (Ipswich)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>29 673</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>28 771</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr">
         <is>
           <t>1</t>
@@ -45922,10 +49087,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Finnie W.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>17 151</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
           <t>3</t>
@@ -46158,10 +49341,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>16 322</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
           <t>0</t>
@@ -46394,10 +49595,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Martin S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Hillsborough
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>39 732</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>32 041</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>1</t>
@@ -46630,10 +49849,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>30 347</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
           <t>3</t>
@@ -46866,10 +50103,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>15 327</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
           <t>1</t>
@@ -47102,10 +50357,28 @@
           <t>13.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>The Hawthorns
+ (West Bromwich)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>26 688</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>25 366</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
           <t>0</t>
@@ -47346,10 +50619,28 @@
           <t>13.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>36 518</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
           <t>0</t>
@@ -47582,10 +50873,28 @@
           <t>12.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Home Park
+ (Plymouth)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>16 861</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
           <t>1</t>
@@ -47818,10 +51127,28 @@
           <t>10.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Stroud K.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>14 692</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
           <t>3</t>
@@ -48054,10 +51381,28 @@
           <t>10.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Eltringham G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>The Hawthorns
+ (West Bromwich)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>26 688</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>22 331</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr">
         <is>
           <t>2</t>
@@ -48290,10 +51635,28 @@
           <t>10.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>St. Andrew's Stadium
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>29 409</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>20 894</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
           <t>0</t>
@@ -48526,10 +51889,28 @@
           <t>10.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Madley R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Ashton Gate Stadium
+ (Bristol)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>19 672</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>5</t>
@@ -48762,10 +52143,28 @@
           <t>10.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>25 586</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>21 934</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t>2</t>
@@ -48998,10 +52397,28 @@
           <t>10.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Portman Road
+ (Ipswich)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>29 673</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>28 589</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
           <t>0</t>
@@ -49234,10 +52651,28 @@
           <t>09.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>36 793</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
           <t>0</t>
@@ -49470,10 +52905,28 @@
           <t>09.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Gill S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>14 889</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr">
         <is>
           <t>1</t>
@@ -49706,10 +53159,28 @@
           <t>09.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Simpson J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Home Park
+ (Plymouth)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>16 928</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
           <t>1</t>
@@ -49942,10 +53413,28 @@
           <t>09.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Smith L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>14 698</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
           <t>4</t>
@@ -50178,10 +53667,28 @@
           <t>09.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Kavanagh C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Hillsborough
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>39 732</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>28 516</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>2</t>
@@ -50414,10 +53921,28 @@
           <t>09.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Linington J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>28 564</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t>2</t>
@@ -50650,10 +54175,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>15 679</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t>0</t>
@@ -50886,10 +54429,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Busby J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>20 688</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>1</t>
@@ -51122,10 +54683,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Nield T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Coventry Building Society Arena
+ (Coventry)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>32 753</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>30 232</t>
+        </is>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
           <t>2</t>
@@ -51358,10 +54937,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Linington J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>John Smith's Stadium
+ (Huddersfield)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>24 121</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>18 569</t>
+        </is>
+      </c>
       <c r="G202" t="inlineStr">
         <is>
           <t>1</t>
@@ -51594,10 +55191,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>32 261</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>31 825</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr">
         <is>
           <t>2</t>
@@ -51830,10 +55445,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Welch R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>24 780</t>
+        </is>
+      </c>
       <c r="G204" t="inlineStr">
         <is>
           <t>2</t>
@@ -52066,10 +55699,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Scott G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>17 502</t>
+        </is>
+      </c>
       <c r="G205" t="inlineStr">
         <is>
           <t>0</t>
@@ -52302,10 +55953,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>22 339</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
           <t>2</t>
@@ -52538,10 +56207,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Stadium of Light
+ (Sunderland)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>48 707</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>40 298</t>
+        </is>
+      </c>
       <c r="G207" t="inlineStr">
         <is>
           <t>0</t>
@@ -52774,10 +56461,28 @@
           <t>06.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>22 200</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>19 374</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr">
         <is>
           <t>0</t>
@@ -53010,10 +56715,28 @@
           <t>06.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Carrow Road
+ (Norwich)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>27 137</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>27 001</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t>1</t>
@@ -53246,10 +56969,28 @@
           <t>05.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Aesseal New York Stadium
+ (Rotherham)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>12 021</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>9 863</t>
+        </is>
+      </c>
       <c r="G210" t="inlineStr">
         <is>
           <t>0</t>
@@ -53474,10 +57215,28 @@
           <t>01.04.2024 16:00</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>36 747</t>
+        </is>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>3</t>
@@ -53710,10 +57469,28 @@
           <t>01.04.2024 13:30</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Salisbury M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Portman Road
+ (Ipswich)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>29 673</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>29 393</t>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
           <t>3</t>
@@ -53954,10 +57731,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>St. Andrew's Stadium
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>29 409</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>24 511</t>
+        </is>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
           <t>1</t>
@@ -54190,10 +57985,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Coventry Building Society Arena
+ (Coventry)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>32 753</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>28 529</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
           <t>1</t>
@@ -54426,10 +58239,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>27 893</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr">
         <is>
           <t>2</t>
@@ -54662,10 +58493,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Stroud K.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Home Park
+ (Plymouth)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>16 866</t>
+        </is>
+      </c>
       <c r="G216" t="inlineStr">
         <is>
           <t>0</t>
@@ -54906,10 +58755,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Chilowicz A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Aesseal New York Stadium
+ (Rotherham)</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>12 021</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>9 803</t>
+        </is>
+      </c>
       <c r="G217" t="inlineStr">
         <is>
           <t>2</t>
@@ -55142,10 +59009,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Simpson J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>23 917</t>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
           <t>1</t>
@@ -55378,10 +59263,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Busby J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Stadium of Light
+ (Sunderland)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>48 707</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>42 019</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr">
         <is>
           <t>1</t>
@@ -55606,10 +59509,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>19 704</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
           <t>0</t>
@@ -55834,10 +59755,28 @@
           <t>01.04.2024 11:00</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>The Hawthorns
+ (West Bromwich)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>26 688</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>24 173</t>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t>2</t>
@@ -56070,10 +60009,28 @@
           <t>01.04.2024 08:30</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Bond D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>32 261</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>31 825</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t>3</t>
@@ -56306,10 +60263,28 @@
           <t>29.03.2024 17:00</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>22 200</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>20 236</t>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>2</t>
@@ -56534,10 +60509,28 @@
           <t>29.03.2024 14:30</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>18 235</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>0</t>
@@ -56770,10 +60763,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Simpson J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>22 141</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>0</t>
@@ -57014,10 +61025,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Herczeg A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>John Smith's Stadium
+ (Huddersfield)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>24 121</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>20 530</t>
+        </is>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
           <t>1</t>
@@ -57250,10 +61279,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Scott G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>25 586</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>24 601</t>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
           <t>0</t>
@@ -57486,10 +61533,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Linington J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Carrow Road
+ (Norwich)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>27 137</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>26 622</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t>2</t>
@@ -57722,10 +61787,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Martin S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>15 470</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t>3</t>
@@ -57958,10 +62041,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>17 170</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr">
         <is>
           <t>2</t>
@@ -58194,10 +62295,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Eltringham G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Hillsborough
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>39 732</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>28 301</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
           <t>1</t>
@@ -58438,10 +62557,28 @@
           <t>29.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>30 470</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr">
         <is>
           <t>1</t>
@@ -58674,10 +62811,28 @@
           <t>29.03.2024 10:00</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>17 856</t>
+        </is>
+      </c>
       <c r="G233" t="inlineStr">
         <is>
           <t>1</t>
@@ -58910,10 +63065,28 @@
           <t>29.03.2024 09:30</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Ashton Gate Stadium
+ (Bristol)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>25 857</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr">
         <is>
           <t>1</t>
@@ -59146,10 +63319,28 @@
           <t>17.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Martin S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>34 813</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr">
         <is>
           <t>2</t>
@@ -59382,10 +63573,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>St. Andrew's Stadium
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>29 409</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>21 266</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
           <t>0</t>
@@ -59618,10 +63827,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Portman Road
+ (Ipswich)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>29 673</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>29 325</t>
+        </is>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
           <t>6</t>
@@ -59854,10 +64081,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Stroud K.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>25 554</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr">
         <is>
           <t>0</t>
@@ -60098,10 +64343,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Busby J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Home Park
+ (Plymouth)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>16 646</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr">
         <is>
           <t>0</t>
@@ -60334,10 +64597,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Aesseal New York Stadium
+ (Rotherham)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>12 021</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>11 033</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr">
         <is>
           <t>0</t>
@@ -60578,10 +64859,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>21 887</t>
+        </is>
+      </c>
       <c r="G241" t="inlineStr">
         <is>
           <t>0</t>
@@ -60814,10 +65113,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Stadium of Light
+ (Sunderland)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>48 707</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>41 478</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
           <t>0</t>
@@ -61050,10 +65367,28 @@
           <t>16.03.2024 12:00</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Nield T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>The Hawthorns
+ (West Bromwich)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>26 688</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>25 254</t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
           <t>2</t>
@@ -61286,10 +65621,28 @@
           <t>16.03.2024 09:30</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>20 005</t>
+        </is>
+      </c>
       <c r="G244" t="inlineStr">
         <is>
           <t>2</t>

--- a/p6_deployment/data/england/missing/data_understanding/all/df_match_miss.xlsx
+++ b/p6_deployment/data/england/missing/data_understanding/all/df_match_miss.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>6HLBNw1</t>
+          <t>6HLBNw1o</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -22412,7 +22412,7 @@
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -23236,7 +23236,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -24358,7 +24358,7 @@
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -24636,7 +24636,7 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -24904,7 +24904,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -25470,7 +25470,7 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
@@ -25738,7 +25738,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -25748,7 +25748,7 @@
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -26012,7 +26012,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -26300,7 +26300,7 @@
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
@@ -26568,7 +26568,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -27132,7 +27132,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
@@ -27688,7 +27688,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
@@ -28252,7 +28252,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -28262,7 +28262,7 @@
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -28540,7 +28540,7 @@
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -29382,7 +29382,7 @@
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -30216,7 +30216,7 @@
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
@@ -30480,7 +30480,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -30490,7 +30490,7 @@
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
@@ -30766,7 +30766,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -31054,7 +31054,7 @@
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
@@ -31322,7 +31322,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
@@ -31600,7 +31600,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -31888,7 +31888,7 @@
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
@@ -32156,7 +32156,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
@@ -32434,7 +32434,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -32722,7 +32722,7 @@
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
@@ -32990,7 +32990,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -33278,7 +33278,7 @@
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -33556,7 +33556,7 @@
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -33834,7 +33834,7 @@
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
@@ -34102,7 +34102,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
@@ -34658,7 +34658,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -34668,7 +34668,7 @@
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
@@ -34937,7 +34937,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
@@ -35248,7 +35248,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
@@ -35559,7 +35559,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -35569,7 +35569,7 @@
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
@@ -35870,7 +35870,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
@@ -36189,7 +36189,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -36199,7 +36199,7 @@
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
@@ -36508,7 +36508,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -36518,7 +36518,7 @@
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
@@ -36819,7 +36819,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -36829,7 +36829,7 @@
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
@@ -37098,7 +37098,7 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
@@ -37353,7 +37353,7 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -37363,7 +37363,7 @@
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
@@ -37608,7 +37608,7 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -37618,7 +37618,7 @@
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
@@ -37862,7 +37862,7 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -37872,7 +37872,7 @@
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
@@ -38116,7 +38116,7 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
@@ -38370,7 +38370,7 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
@@ -38624,7 +38624,7 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
@@ -38878,7 +38878,7 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -38888,7 +38888,7 @@
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
@@ -39132,7 +39132,7 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -39142,7 +39142,7 @@
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
@@ -39386,7 +39386,7 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -39396,7 +39396,7 @@
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
@@ -39640,7 +39640,7 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
@@ -39886,7 +39886,7 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -39896,7 +39896,7 @@
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
@@ -40140,7 +40140,7 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>zNcAe8S</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -40150,7 +40150,7 @@
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
@@ -40386,7 +40386,7 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -40396,7 +40396,7 @@
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
@@ -40640,7 +40640,7 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
@@ -40894,7 +40894,7 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
@@ -41156,7 +41156,7 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
@@ -41413,7 +41413,7 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
@@ -41667,7 +41667,7 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -41677,7 +41677,7 @@
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
@@ -41921,7 +41921,7 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
@@ -42175,7 +42175,7 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -42185,7 +42185,7 @@
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
@@ -42437,7 +42437,7 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -42447,7 +42447,7 @@
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>zNcAe8S</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
@@ -42683,7 +42683,7 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -42693,7 +42693,7 @@
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
@@ -42937,7 +42937,7 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
@@ -43183,7 +43183,7 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -43193,7 +43193,7 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
@@ -43437,7 +43437,7 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -43691,7 +43691,7 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -43701,7 +43701,7 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -43945,7 +43945,7 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -43955,7 +43955,7 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
@@ -44199,7 +44199,7 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -44209,7 +44209,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -44453,7 +44453,7 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -44463,7 +44463,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -44707,7 +44707,7 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
@@ -44961,7 +44961,7 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -44971,7 +44971,7 @@
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
@@ -45215,7 +45215,7 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -45225,7 +45225,7 @@
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
@@ -45469,7 +45469,7 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -45479,7 +45479,7 @@
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
@@ -45723,7 +45723,7 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -45733,7 +45733,7 @@
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
@@ -45977,7 +45977,7 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -45987,7 +45987,7 @@
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
@@ -46231,7 +46231,7 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -46241,7 +46241,7 @@
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
@@ -46485,7 +46485,7 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -46495,7 +46495,7 @@
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
@@ -46739,7 +46739,7 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>zNcAe8S</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
@@ -46993,7 +46993,7 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -47003,7 +47003,7 @@
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
@@ -47247,7 +47247,7 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -47257,7 +47257,7 @@
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
@@ -47501,7 +47501,7 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -47511,7 +47511,7 @@
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
@@ -47755,7 +47755,7 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -47765,7 +47765,7 @@
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
@@ -48009,7 +48009,7 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -48019,7 +48019,7 @@
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
@@ -48263,7 +48263,7 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -48273,7 +48273,7 @@
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
@@ -48517,7 +48517,7 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -48527,7 +48527,7 @@
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
@@ -48771,7 +48771,7 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -48781,7 +48781,7 @@
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
@@ -49025,7 +49025,7 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -49035,7 +49035,7 @@
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
@@ -49279,7 +49279,7 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -49289,7 +49289,7 @@
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
@@ -49533,7 +49533,7 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -49543,7 +49543,7 @@
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
@@ -49787,7 +49787,7 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -49797,7 +49797,7 @@
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
@@ -50041,7 +50041,7 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -50051,7 +50051,7 @@
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
@@ -50295,7 +50295,7 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -50305,7 +50305,7 @@
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
@@ -50549,7 +50549,7 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -50559,7 +50559,7 @@
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
@@ -50811,7 +50811,7 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -50821,7 +50821,7 @@
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
@@ -51065,7 +51065,7 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -51075,7 +51075,7 @@
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
@@ -51319,7 +51319,7 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -51329,7 +51329,7 @@
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
@@ -51573,7 +51573,7 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -51583,7 +51583,7 @@
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
@@ -51827,7 +51827,7 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -51837,7 +51837,7 @@
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
@@ -52081,7 +52081,7 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -52091,7 +52091,7 @@
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
@@ -52335,7 +52335,7 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -52345,7 +52345,7 @@
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
@@ -52589,7 +52589,7 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
@@ -52599,7 +52599,7 @@
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
@@ -52843,7 +52843,7 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
@@ -52853,7 +52853,7 @@
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
@@ -53097,7 +53097,7 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -53107,7 +53107,7 @@
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
@@ -53351,7 +53351,7 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -53361,7 +53361,7 @@
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
@@ -53605,7 +53605,7 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -53615,7 +53615,7 @@
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
@@ -53859,7 +53859,7 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -53869,7 +53869,7 @@
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
@@ -54113,7 +54113,7 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -54123,7 +54123,7 @@
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
@@ -54367,7 +54367,7 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -54377,7 +54377,7 @@
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
@@ -54621,7 +54621,7 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -54631,7 +54631,7 @@
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
@@ -54875,7 +54875,7 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -54885,7 +54885,7 @@
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
@@ -55129,7 +55129,7 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -55139,7 +55139,7 @@
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
@@ -55383,7 +55383,7 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -55393,7 +55393,7 @@
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
@@ -55637,7 +55637,7 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -55647,7 +55647,7 @@
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
@@ -55891,7 +55891,7 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
@@ -56145,7 +56145,7 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -56155,7 +56155,7 @@
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
@@ -56399,7 +56399,7 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -56409,7 +56409,7 @@
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
@@ -56653,7 +56653,7 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -56663,7 +56663,7 @@
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
@@ -56907,7 +56907,7 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -56917,7 +56917,7 @@
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
@@ -57153,7 +57153,7 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -57163,7 +57163,7 @@
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
@@ -57407,7 +57407,7 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -57417,7 +57417,7 @@
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
@@ -57661,7 +57661,7 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -57671,7 +57671,7 @@
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
@@ -57923,7 +57923,7 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -57933,7 +57933,7 @@
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
@@ -58177,7 +58177,7 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -58187,7 +58187,7 @@
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
@@ -58431,7 +58431,7 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
@@ -58685,7 +58685,7 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>nglXJS0</t>
+          <t>nglXJS0e</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -58695,7 +58695,7 @@
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
@@ -58947,7 +58947,7 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -58957,7 +58957,7 @@
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
@@ -59201,7 +59201,7 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -59211,7 +59211,7 @@
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
@@ -59447,7 +59447,7 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -59457,7 +59457,7 @@
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
@@ -59693,7 +59693,7 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -59703,7 +59703,7 @@
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
@@ -59947,7 +59947,7 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -59957,7 +59957,7 @@
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
@@ -60201,7 +60201,7 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -60211,7 +60211,7 @@
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
@@ -60447,7 +60447,7 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
@@ -60457,7 +60457,7 @@
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
@@ -60701,7 +60701,7 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -60711,7 +60711,7 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
@@ -60963,7 +60963,7 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -60973,7 +60973,7 @@
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
@@ -61217,7 +61217,7 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -61227,7 +61227,7 @@
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
@@ -61471,7 +61471,7 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -61481,7 +61481,7 @@
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
@@ -61725,7 +61725,7 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -61735,7 +61735,7 @@
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>nglXJS0</t>
+          <t>nglXJS0e</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
@@ -61979,7 +61979,7 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
@@ -61989,7 +61989,7 @@
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
@@ -62233,7 +62233,7 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
@@ -62243,7 +62243,7 @@
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
@@ -62495,7 +62495,7 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
@@ -62505,7 +62505,7 @@
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
@@ -62749,7 +62749,7 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
@@ -62759,7 +62759,7 @@
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
@@ -63003,7 +63003,7 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -63013,7 +63013,7 @@
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
@@ -63257,7 +63257,7 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -63267,7 +63267,7 @@
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
@@ -63511,7 +63511,7 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -63521,7 +63521,7 @@
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
@@ -63765,7 +63765,7 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>joMpXpx</t>
+          <t>joMpXpxG</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -63775,7 +63775,7 @@
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
@@ -64019,7 +64019,7 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
@@ -64029,7 +64029,7 @@
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
@@ -64281,7 +64281,7 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
@@ -64291,7 +64291,7 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
@@ -64535,7 +64535,7 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>nglXJS0</t>
+          <t>nglXJS0e</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -64545,7 +64545,7 @@
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
@@ -64789,7 +64789,7 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
@@ -65051,7 +65051,7 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -65061,7 +65061,7 @@
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
@@ -65305,7 +65305,7 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
@@ -65315,7 +65315,7 @@
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
@@ -65559,7 +65559,7 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
@@ -65569,7 +65569,7 @@
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
@@ -65813,7 +65813,7 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
@@ -65823,7 +65823,7 @@
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
